--- a/tests/fixtures/dimensions/dimensions.xlsx
+++ b/tests/fixtures/dimensions/dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76B54413-777B-4A18-BE70-5055C5EFF90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75187690-C07E-4871-A004-F960316E8A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="19440" windowHeight="11220" xr2:uid="{C89A758C-9964-4C2F-B758-D3EA2E165644}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="19440" windowHeight="11220" xr2:uid="{8D295F94-FA50-47BA-B7C1-869EED3CA05B}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_rows" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,8 @@
     <sheet name="show_one_of_every_row" sheetId="17" r:id="rId17"/>
     <sheet name="hide_rows_to_the_end" sheetId="18" r:id="rId18"/>
     <sheet name="hide_every_column" sheetId="19" r:id="rId19"/>
+    <sheet name="font_rows" sheetId="20" r:id="rId20"/>
+    <sheet name="recorded_rows" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,9 +58,21 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>x
+y</t>
+  </si>
+  <si>
+    <t>turned</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +87,83 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="40"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="30"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12.4"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Segoe Print"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe Print"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,9 +186,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,7 +540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D130DCAD-469A-45C9-AAC7-3D4F0F355B37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DE4867-122F-4F6D-ABAF-28ED04A2E5E2}">
   <dimension ref="A2:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -448,7 +557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E381EA6B-AB76-4C63-B462-04A4431EFA99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8AADEA-5362-4ADD-8109-E6393BAEBB35}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -457,7 +566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74CADF1-3050-4DEA-B949-83B2272114BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D671E6-A877-47AB-A999-66F6FDA0839A}">
   <dimension ref="A2:E20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -485,7 +594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B227C4F9-2787-4FBD-B907-5A0B3992E1D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615FFC40-CED7-478C-80B8-11F488CB4BBF}">
   <dimension ref="A3:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -498,7 +607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C450E27-BB4A-42C7-9314-15EED33EC134}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97A6CE1-4DB3-4FC6-86A4-C0D56070046C}">
   <dimension ref="A3:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -511,7 +620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A29BD09-EE1A-41E4-944C-2353A08F485F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444F66E4-B5B2-41C6-A8A4-9C5575BB5FBD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -524,7 +633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D2AF88-65C0-4E51-BAB3-7D071DEE48CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98AC7550-23DE-49BD-829C-DDA0C7A91247}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -533,7 +642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF3F2FB0-CC5A-4CEC-B647-1488D26D37E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4C6512-11A3-44B4-9AF5-95CCFCED267C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -542,7 +651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42ED3717-E0B8-478F-AC65-EC9276E52F03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F0E3CF-DBD6-4CDE-8C50-D570387477A2}">
   <dimension ref="A5"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -553,7 +662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5970D8-3EE5-48F6-BB34-120E1006DF21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984FA279-CB41-4FF0-84B5-0F6326692BF4}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -565,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14ACB64A-71F9-46DA-9892-7A844F5CC3C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3820FDAD-B850-463A-9BE4-0D197C9F6209}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -579,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E54FD5-ECF4-44FE-884B-A476DEB14507}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3E2B12-A550-4017-8C4F-1F6511FCDAC5}">
   <dimension ref="A2:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -594,8 +703,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E63B07-9FF0-4913-822F-7EB8A665A306}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" ht="26.25" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" ht="49.5" x14ac:dyDescent="0.65">
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8516A53D-4765-4575-8981-067A5A130989}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="33" x14ac:dyDescent="0.45">
+      <c r="A1" s="2"/>
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2" ht="41.25" x14ac:dyDescent="1.05">
+      <c r="A2" s="11"/>
+    </row>
+    <row r="3" spans="1:2" ht="29.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="12"/>
+    </row>
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="35.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.45">
+      <c r="A6" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04394A3-704F-4F34-914A-FA1683922907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4B09BF-A4F6-4A2F-BE2C-006DD1365D08}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -612,7 +795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{952F0676-3397-4247-861E-10211F1D9CFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC88309-597F-4BBF-B90F-DE83791C7400}">
   <dimension ref="B1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -628,7 +811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33EE2C3-882A-4ECD-84C3-CB93523BAE48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBBDB70-F7E0-45C2-B79A-ACC485C875E1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -640,7 +823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A3812D-75B1-4040-A079-9BADCEB07B68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC6507BF-5FDE-4BAB-BB13-0978C8B24552}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -649,7 +832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83660914-193F-42ED-860B-847CBBFEC019}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B104929D-0410-4AEE-B535-D117F829FFF7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -658,7 +841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749C3475-092F-4C18-B0C6-EA9BE63FCFA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58611625-D7E2-4ECC-A2F5-FFE73FA116F9}">
   <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -670,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C3B7D2-DBE5-4D44-BD15-0B4342D5642D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F89460AF-E8A2-41F1-9A03-1E549E01D50B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/tests/fixtures/dimensions/dimensions.xlsx
+++ b/tests/fixtures/dimensions/dimensions.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\dimensions\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{75187690-C07E-4871-A004-F960316E8A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="19440" windowHeight="11220" xr2:uid="{8D295F94-FA50-47BA-B7C1-869EED3CA05B}"/>
